--- a/output/full_scan/batch_seq8_2026-08-27.xlsx
+++ b/output/full_scan/batch_seq8_2026-08-27.xlsx
@@ -538,7 +538,7 @@
         <v/>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1017.209794294528</v>
+        <v>1187.209794294528</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>158</v>
@@ -552,10 +552,10 @@
         <v>0</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>71.5246186500346</v>
+        <v>71.52461859997975</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>23.04385523430997</v>
+        <v>23.04385524148593</v>
       </c>
       <c r="J2" s="2" t="n">
         <v>2.291163628726688</v>
@@ -570,31 +570,31 @@
         <v>-1</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>0.3212925794196435</v>
+        <v>0.3212925784656697</v>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
-        <v>6936</v>
+        <v>7788</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>永鴻生技</t>
+          <t>松川精密</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
         <v/>
       </c>
       <c r="D3" s="2" t="n">
-        <v>911.4449957201928</v>
+        <v>1038.31193559685</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>33.1</v>
+        <v>298</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
@@ -605,16 +605,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>63.74103945487474</v>
+        <v>67.45574368458992</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>27.82898614540119</v>
+        <v>25.11194606249304</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>1.517426649312956</v>
+        <v>2.643295447138091</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
         <v>0</v>
@@ -623,51 +623,51 @@
         <v>-1</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>0.10470432606159</v>
+        <v>3.657015831516194</v>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
-        <v>6949</v>
+        <v>7556</v>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沛爾生醫-創</t>
+          <t>意德士</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
         <v/>
       </c>
       <c r="D4" s="2" t="n">
-        <v>903.850713129944</v>
+        <v>1009.471572290126</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1490</v>
+        <v>264</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G4" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>84.44665559927209</v>
+        <v>67.04671611416776</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>38.6367390440172</v>
+        <v>27.0242405096473</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>1.896361293282596</v>
+        <v>2.615077305572802</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L4" s="2" t="n">
         <v>0</v>
@@ -676,31 +676,31 @@
         <v>-1</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>44.09810044617502</v>
+        <v>4.100919215182585</v>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
-        <v>7556</v>
+        <v>8039</v>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>意德士</t>
+          <t>台虹</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
         <v/>
       </c>
       <c r="D5" s="2" t="n">
-        <v>869.4715722901261</v>
+        <v>974.1031273730476</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>264</v>
+        <v>352.5</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
@@ -711,49 +711,49 @@
         <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>67.04671614282424</v>
+        <v>74.40251166559887</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>27.0242405096473</v>
+        <v>37.08413845484192</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.615077305572802</v>
+        <v>0.6517602344855163</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>4.100919215087202</v>
+        <v>7.336009272739723</v>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
-        <v>7788</v>
+        <v>6918</v>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>松川精密</t>
+          <t>愛派司</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
         <v/>
       </c>
       <c r="D6" s="2" t="n">
-        <v>828.3119355968497</v>
+        <v>949.8293075053118</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>298</v>
+        <v>78</v>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
@@ -764,16 +764,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>67.45574370954873</v>
+        <v>69.89754162526889</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>25.11194603811543</v>
+        <v>30.92839277158253</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>2.643295447138091</v>
+        <v>2.941589855598002</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>0</v>
@@ -782,31 +782,31 @@
         <v>-1</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3.657015832183964</v>
+        <v>0.3997545223663502</v>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>7714</v>
+        <v>6936</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>創泓科技</t>
+          <t>永鴻生技</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>817.1806973489511</v>
+        <v>931.4449957201909</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>184</v>
+        <v>33.1</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,16 +817,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>60.17112804566057</v>
+        <v>63.74103948291553</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>25.1769484586523</v>
+        <v>27.82898614756176</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.118380768556624</v>
+        <v>1.517426649312956</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" s="2" t="n">
         <v>0</v>
@@ -835,31 +835,31 @@
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>2.244670031675374</v>
+        <v>0.1047043260329715</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>6918</v>
+        <v>6887</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>愛派司</t>
+          <t>寶綠特-KY</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>789.8293075053118</v>
+        <v>908.0841048995726</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>78</v>
+        <v>39.45</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,16 +870,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>69.8975413507857</v>
+        <v>61.07471313047712</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>30.92839274930096</v>
+        <v>24.06340420854085</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>2.941589855598002</v>
+        <v>3.786756507767016</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L8" s="2" t="n">
         <v>0</v>
@@ -888,48 +888,48 @@
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.3997545230150615</v>
+        <v>0.2648308032248584</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
-        <v>7799</v>
+        <v>6949</v>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>禾榮科</t>
+          <t>沛爾生醫-創</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
         <v/>
       </c>
       <c r="D9" s="2" t="n">
-        <v>757.904575910363</v>
+        <v>903.850713129944</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>383.5</v>
+        <v>1490</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="G9" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>55.88543436445002</v>
+        <v>84.4466555953699</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>14.8351240766877</v>
+        <v>38.63673907322983</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.313615810112626</v>
+        <v>1.896361293282596</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>0</v>
@@ -941,31 +941,31 @@
         <v>-1</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>3.210760506662057</v>
+        <v>44.09810044627819</v>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
-        <v>6887</v>
+        <v>7751</v>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>寶綠特-KY</t>
+          <t>竑騰</t>
         </is>
       </c>
       <c r="C10" s="2" t="n">
         <v/>
       </c>
       <c r="D10" s="2" t="n">
-        <v>738.0841048995725</v>
+        <v>901.9844991901108</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>39.45</v>
+        <v>1985</v>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
@@ -976,49 +976,49 @@
         <v>0</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>61.07471317975311</v>
+        <v>72.54159401913381</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>24.06340419313173</v>
+        <v>21.16731364399449</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>3.786756507767016</v>
+        <v>1.179446847320283</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>0.264830803186699</v>
+        <v>59.21758025951682</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>7822</v>
+        <v>6933</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>倍利科</t>
+          <t>AMAX-KY</t>
         </is>
       </c>
       <c r="C11" s="2" t="n">
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>703.8238538357326</v>
+        <v>882.6222879814879</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>957</v>
+        <v>236.5</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1029,13 +1029,13 @@
         <v>0</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>57.91414370633398</v>
+        <v>75.45636533084071</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>14.07564507560212</v>
+        <v>22.21884225519491</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>1.525542247215195</v>
+        <v>0.8622287981487907</v>
       </c>
       <c r="K11" s="2" t="n">
         <v>0</v>
@@ -1047,31 +1047,31 @@
         <v>-1</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>15.36269028416824</v>
+        <v>3.736702821034619</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>7751</v>
+        <v>6906</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>竑騰</t>
+          <t>現觀科</t>
         </is>
       </c>
       <c r="C12" s="2" t="n">
         <v/>
       </c>
       <c r="D12" s="2" t="n">
-        <v>701.9844991901098</v>
+        <v>875.3800825814042</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1985</v>
+        <v>75.3</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
@@ -1082,49 +1082,49 @@
         <v>0</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>72.54159401484102</v>
+        <v>56.125690147515</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>21.16731354930498</v>
+        <v>17.34662288192203</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>1.179446847320283</v>
+        <v>1.703290217043021</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L12" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N12" s="2" t="n">
-        <v>59.21758026094767</v>
+        <v>0.6677800782210608</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, invest_trust_buy_2d, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>7744</v>
+        <v>6840</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>崴寶</t>
+          <t>東研信超</t>
         </is>
       </c>
       <c r="C13" s="2" t="n">
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>681.4619675178693</v>
+        <v>855.4267605072356</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>503</v>
+        <v>98.3</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
@@ -1135,16 +1135,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>60.20547606752364</v>
+        <v>87.5212560708421</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>29.64451640883789</v>
+        <v>37.12377384667572</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.499747882641506</v>
+        <v>2.642676050723557</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L13" s="2" t="n">
         <v>0</v>
@@ -1153,31 +1153,31 @@
         <v>-1</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>3.418038511671821</v>
+        <v>1.956280185444912</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>7795</v>
+        <v>7714</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>長廣</t>
+          <t>創泓科技</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>677.1282911909525</v>
+        <v>817.1806973489511</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>545</v>
+        <v>184</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
@@ -1188,13 +1188,13 @@
         <v>0</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>56.59895671757658</v>
+        <v>60.17112810999229</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>27.56468255213786</v>
+        <v>25.17694846248234</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>1.190480306454403</v>
+        <v>2.118380768556624</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>0</v>
@@ -1206,31 +1206,31 @@
         <v>-1</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>6.227115226485505</v>
+        <v>2.244670031179313</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>6840</v>
+        <v>7810</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>東研信超</t>
+          <t>捷創科技</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>655.4267605072356</v>
+        <v>816.5739551634788</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>98.3</v>
+        <v>219</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>87.52125606715356</v>
+        <v>68.60972925897275</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>37.12377387014937</v>
+        <v>27.6955917528901</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>2.642676050723557</v>
+        <v>1.151108249491708</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>1.956280185444912</v>
+        <v>3.036969663243804</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>7810</v>
+        <v>7822</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>捷創科技</t>
+          <t>倍利科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>646.5739551634788</v>
+        <v>813.8238538357327</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>219</v>
+        <v>957</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,13 +1294,13 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>68.6097292853441</v>
+        <v>57.91414373114819</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>27.69559176526044</v>
+        <v>14.075645241636</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.151108249491708</v>
+        <v>1.525542247215195</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>3</v>
@@ -1312,31 +1312,31 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.036969663396445</v>
+        <v>15.36269027977989</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, foreign_buy_3d, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>6957</v>
+        <v>7711</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>裕慶-KY</t>
+          <t>永擎</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
         <v/>
       </c>
       <c r="D17" s="2" t="n">
-        <v>642.4203429590248</v>
+        <v>807.1126856418117</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>225</v>
+        <v>493</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
@@ -1347,16 +1347,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>58.46020003534967</v>
+        <v>67.44997643877824</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>13.4571725575023</v>
+        <v>45.67857215434904</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>1.080799837948896</v>
+        <v>0.7666402943503439</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" s="2" t="n">
         <v>0</v>
@@ -1365,31 +1365,31 @@
         <v>-1</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>0.3810787931306813</v>
+        <v>4.251588853173544</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>7711</v>
+        <v>6983</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>永擎</t>
+          <t>華洋精機</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
         <v/>
       </c>
       <c r="D18" s="2" t="n">
-        <v>637.1126856418118</v>
+        <v>783.4768680693135</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>493</v>
+        <v>337.5</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
@@ -1400,13 +1400,13 @@
         <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>67.4499764407814</v>
+        <v>61.93927184107202</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>45.67857210744267</v>
+        <v>10.93296102765692</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>0.7666402943503439</v>
+        <v>3.947686806931348</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>0</v>
@@ -1418,31 +1418,31 @@
         <v>-1</v>
       </c>
       <c r="N18" s="2" t="n">
-        <v>4.251588852982792</v>
+        <v>5.005459838086571</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>6906</v>
+        <v>6957</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>現觀科</t>
+          <t>裕慶-KY</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
         <v/>
       </c>
       <c r="D19" s="2" t="n">
-        <v>625.3800825814042</v>
+        <v>782.4203429590248</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>75.3</v>
+        <v>225</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1453,16 +1453,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>56.1256900605401</v>
+        <v>58.46019998720998</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>17.34662293935003</v>
+        <v>13.45717254903866</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>1.703290217043021</v>
+        <v>1.080799837948896</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L19" s="2" t="n">
         <v>0</v>
@@ -1471,31 +1471,31 @@
         <v>-1</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>0.6677800787934447</v>
+        <v>0.3810787928445073</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, hist_turn_positive, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>6933</v>
+        <v>7799</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>AMAX-KY</t>
+          <t>禾榮科</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
         <v/>
       </c>
       <c r="D20" s="2" t="n">
-        <v>617.6222879814879</v>
+        <v>777.904575910363</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>236.5</v>
+        <v>383.5</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
@@ -1506,16 +1506,16 @@
         <v>0</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>75.4563652979888</v>
+        <v>55.88543496738546</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>22.21884224808597</v>
+        <v>14.83512404258888</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>0.8622287981487907</v>
+        <v>2.313615810112626</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L20" s="2" t="n">
         <v>0</v>
@@ -1524,31 +1524,31 @@
         <v>-1</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>3.736702822083979</v>
+        <v>3.210760491398529</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>6983</v>
+        <v>7402</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>華洋精機</t>
+          <t>邑錡</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
         <v/>
       </c>
       <c r="D21" s="2" t="n">
-        <v>613.4768680693135</v>
+        <v>777.2162962641574</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>337.5</v>
+        <v>117.5</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
@@ -1559,16 +1559,16 @@
         <v>0</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>61.9392718153741</v>
+        <v>58.65986515086895</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>10.93296102718624</v>
+        <v>19.09237330207365</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.947686806931348</v>
+        <v>5.842255019078944</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" s="2" t="n">
         <v>0</v>
@@ -1577,31 +1577,31 @@
         <v>-1</v>
       </c>
       <c r="N21" s="2" t="n">
-        <v>5.005459838659011</v>
+        <v>0.9134261420037648</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, bb_squeeze_breakout, breakout_volume_confirm, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n">
-        <v>7402</v>
+        <v>6922</v>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>邑錡</t>
+          <t>宸曜</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>607.2162962641574</v>
+        <v>739.2028196723812</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>117.5</v>
+        <v>206</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
@@ -1612,13 +1612,13 @@
         <v>0</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>58.65986516680474</v>
+        <v>57.75061029278332</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>19.09237336041166</v>
+        <v>24.81658161977864</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>5.842255019078944</v>
+        <v>0.5954691723476129</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>1</v>
@@ -1630,31 +1630,31 @@
         <v>-1</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>0.9134261421945432</v>
+        <v>0.477285179336409</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, bb_squeeze_breakout, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n">
-        <v>6922</v>
+        <v>6937</v>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>宸曜</t>
+          <t>天虹</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
         <v/>
       </c>
       <c r="D23" s="2" t="n">
-        <v>599.2028196723811</v>
+        <v>712.9198764983455</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>206</v>
+        <v>281</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1665,16 +1665,16 @@
         <v>0</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>57.75061023716487</v>
+        <v>55.46132490250793</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>24.81658155872218</v>
+        <v>8.54485307840854</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>0.5954691723476129</v>
+        <v>0.9092646779741836</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L23" s="2" t="n">
         <v>0</v>
@@ -1683,31 +1683,31 @@
         <v>-1</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>0.4772851798134159</v>
+        <v>0.5020125635354272</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="n">
-        <v>7792</v>
+        <v>7744</v>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>安葆</t>
+          <t>崴寶</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
         <v/>
       </c>
       <c r="D24" s="2" t="n">
-        <v>599.1631853942883</v>
+        <v>681.4619675178693</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>300.5</v>
+        <v>503</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1718,16 +1718,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>72.43186941005754</v>
+        <v>60.20547606219949</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>43.27351130586885</v>
+        <v>29.64451640138361</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>0.7163185394288422</v>
+        <v>1.499747882641506</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L24" s="2" t="n">
         <v>0</v>
@@ -1736,31 +1736,31 @@
         <v>-1</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>7.767048126771918</v>
+        <v>3.418038511862678</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n">
-        <v>7750</v>
+        <v>6953</v>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>新代</t>
+          <t>家碩</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>568.6367464775229</v>
+        <v>678.4582901448924</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2450</v>
+        <v>238.5</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
@@ -1771,16 +1771,16 @@
         <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>56.98147319824956</v>
+        <v>62.21777399713287</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>16.79049604370908</v>
+        <v>16.46509780833702</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>1.163674647752292</v>
+        <v>1.19498694480829</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L25" s="2" t="n">
         <v>0</v>
@@ -1789,31 +1789,31 @@
         <v>-1</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>-6.685463223771549</v>
+        <v>2.153704143808147</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="n">
-        <v>8039</v>
+        <v>7795</v>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>台虹</t>
+          <t>長廣</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
         <v/>
       </c>
       <c r="D26" s="2" t="n">
-        <v>559.1031273730474</v>
+        <v>677.1282911909525</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>352.5</v>
+        <v>545</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
@@ -1824,13 +1824,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>74.40251165939965</v>
+        <v>56.59895671508636</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>37.08413829256416</v>
+        <v>27.56468261522704</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>0.6517602344855163</v>
+        <v>1.190480306454403</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>0</v>
@@ -1842,31 +1842,31 @@
         <v>-1</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>7.336009273121299</v>
+        <v>6.227115226294711</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n">
-        <v>6937</v>
+        <v>7717</v>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>天虹</t>
+          <t>萊德光電-KY</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
         <v/>
       </c>
       <c r="D27" s="2" t="n">
-        <v>552.9198764983454</v>
+        <v>649.3238101522593</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>281</v>
+        <v>434</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
@@ -1877,16 +1877,16 @@
         <v>0</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>55.46132490941802</v>
+        <v>52.68882946288449</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>8.544853061701529</v>
+        <v>14.85246560379053</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>0.9092646779741836</v>
+        <v>1.349612136145119</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L27" s="2" t="n">
         <v>0</v>
@@ -1895,31 +1895,31 @@
         <v>-1</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>0.5020125654433877</v>
+        <v>3.802382286493126</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>6969</v>
+        <v>7750</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>成信實業*-創</t>
+          <t>新代</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>548.4368194085613</v>
+        <v>643.6367464775229</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>34.8</v>
+        <v>2450</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>56.94386844490025</v>
+        <v>56.98147320645309</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>19.75090663549698</v>
+        <v>16.7904960873502</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>0.7943347745802963</v>
+        <v>1.163674647752292</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>-0.1590071425893959</v>
+        <v>-6.685463228350571</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>6953</v>
+        <v>7631</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>家碩</t>
+          <t>聚賢研發-創</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>538.4582901448917</v>
+        <v>643.0618382479214</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>238.5</v>
+        <v>146.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,16 +1983,16 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>62.21777404761637</v>
+        <v>56.90138052166744</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>16.46509776697483</v>
+        <v>22.32387585041012</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.19498694480829</v>
+        <v>0.6736690039918014</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L29" s="2" t="n">
         <v>0</v>
@@ -2001,31 +2001,31 @@
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>2.153704144094348</v>
+        <v>0.6936959481034104</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>7631</v>
+        <v>7730</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>聚賢研發-創</t>
+          <t>暉盛-創</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>533.0618382479214</v>
+        <v>636.7958267093733</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>146.5</v>
+        <v>185</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,16 +2036,16 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>56.90138053058254</v>
+        <v>60.92417767799422</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>22.32387583083284</v>
+        <v>18.55461056539464</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.6736690039918014</v>
+        <v>1.279582670937326</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L30" s="2" t="n">
         <v>0</v>
@@ -2054,31 +2054,31 @@
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>0.6936959480080271</v>
+        <v>3.045062838843982</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>8042</v>
+        <v>7712</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>金山電</t>
+          <t>博盛半導體</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>489.8158337082102</v>
+        <v>630.8465385339707</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>104.5</v>
+        <v>156</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>43.38396135378084</v>
+        <v>55.97510426395545</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>21.98128821764335</v>
+        <v>15.12059269615429</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.9765060452235746</v>
+        <v>1.580207780496045</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>0.8960015135774597</v>
+        <v>2.662596555057724</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>8016</v>
+        <v>8033</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>矽創</t>
+          <t>雷虎</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>485.5876598867982</v>
+        <v>616.6349493171974</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>300</v>
+        <v>199</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,16 +2142,16 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>51.44263050997144</v>
+        <v>55.79996723032061</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>11.31929085675043</v>
+        <v>15.11606032685093</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.4595519873172662</v>
+        <v>3.950316356483855</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>0.0388740368288499</v>
+        <v>1.016809139129375</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>7828</v>
+        <v>8016</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>創新服務</t>
+          <t>矽創</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>485.0290431584445</v>
+        <v>610.5876598867982</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1650</v>
+        <v>300</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>49.15604588181786</v>
+        <v>51.44263057037446</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>11.52958297603176</v>
+        <v>11.3192909056889</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.292600270824689</v>
+        <v>0.4595519873172662</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>0.3655020430105793</v>
+        <v>0.0388740356840795</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>8028</v>
+        <v>8042</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>昇陽半導體</t>
+          <t>金山電</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>479.928158668464</v>
+        <v>604.8158337082102</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>248.5</v>
+        <v>104.5</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,16 +2248,16 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>42.24363888904853</v>
+        <v>43.38396136121743</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>21.68354726007098</v>
+        <v>21.98128828778752</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>0.699188014345717</v>
+        <v>0.9765060452235746</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L34" s="2" t="n">
         <v>0</v>
@@ -2266,31 +2266,31 @@
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>0.2372379547563596</v>
+        <v>0.8960015133675725</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>7717</v>
+        <v>7792</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>萊德光電-KY</t>
+          <t>安葆</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>479.3238101522593</v>
+        <v>599.1631853942883</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>434</v>
+        <v>300.5</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,16 +2301,16 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>52.68882946288449</v>
+        <v>72.43186943801551</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>14.85246560379053</v>
+        <v>43.27351137859644</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.349612136145119</v>
+        <v>0.7163185394288422</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L35" s="2" t="n">
         <v>0</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>3.802382286493126</v>
+        <v>7.767048126199548</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, liquidity_ok, foreign_buy_3d, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>6914</v>
+        <v>7780</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>阜爾運通</t>
+          <t>大研生醫*</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>471.7423680934216</v>
+        <v>575.3313061420853</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>125</v>
+        <v>17.05</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,16 +2354,16 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>21.56827928612839</v>
+        <v>51.40059918903451</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>21.76814810902493</v>
+        <v>23.7182707777466</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>2.274230864834892</v>
+        <v>1.295901960847647</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L36" s="2" t="n">
         <v>0</v>
@@ -2372,31 +2372,31 @@
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>-2.529118197988549</v>
+        <v>0.0797859477371525</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>7780</v>
+        <v>6969</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>大研生醫*</t>
+          <t>成信實業*-創</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>465.3313061420853</v>
+        <v>568.4368194085613</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>17.05</v>
+        <v>34.8</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>51.40060405168944</v>
+        <v>56.94386848912006</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>23.71827040870815</v>
+        <v>19.75090663670806</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>1.295901960847647</v>
+        <v>0.7943347745802963</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,31 +2425,31 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>0.0797859459205503</v>
+        <v>-0.1590071427992665</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
-        <v>8033</v>
+        <v>6895</v>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>雷虎</t>
+          <t>宏碩系統</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
         <v/>
       </c>
       <c r="D38" s="2" t="n">
-        <v>461.6349493171973</v>
+        <v>562.858070482986</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>199</v>
+        <v>147</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
@@ -2460,13 +2460,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>55.79996721060667</v>
+        <v>71.43855198105999</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15.11606027112239</v>
+        <v>21.98057718585413</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>3.950316356483855</v>
+        <v>1.180150374796492</v>
       </c>
       <c r="K38" s="2" t="n">
         <v>0</v>
@@ -2478,31 +2478,31 @@
         <v>-1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>1.016809139282013</v>
+        <v>3.93508145589367</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n">
-        <v>7712</v>
+        <v>6885</v>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>博盛半導體</t>
+          <t>全福生技</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
         <v/>
       </c>
       <c r="D39" s="2" t="n">
-        <v>460.8465385339708</v>
+        <v>555.4202366196</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>156</v>
+        <v>22.65</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
@@ -2513,13 +2513,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>55.9751041710818</v>
+        <v>66.36755276100679</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15.12059263833561</v>
+        <v>20.67196447841912</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.580207780496045</v>
+        <v>7.535213916201021</v>
       </c>
       <c r="K39" s="2" t="n">
         <v>0</v>
@@ -2531,31 +2531,31 @@
         <v>-1</v>
       </c>
       <c r="N39" s="2" t="n">
-        <v>2.662596556297887</v>
+        <v>0.2685360861220457</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="n">
-        <v>6931</v>
+        <v>7728</v>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>青松健康</t>
+          <t>光焱科技</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
         <v/>
       </c>
       <c r="D40" s="2" t="n">
-        <v>456.4921460022534</v>
+        <v>538.4419931705891</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>41.5</v>
+        <v>630</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
@@ -2566,13 +2566,13 @@
         <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>57.67267179230608</v>
+        <v>56.46513633686541</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>29.13464238782952</v>
+        <v>19.78578912698808</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.647291302296907</v>
+        <v>1.794991558806978</v>
       </c>
       <c r="K40" s="2" t="n">
         <v>0</v>
@@ -2584,31 +2584,31 @@
         <v>-1</v>
       </c>
       <c r="N40" s="2" t="n">
-        <v>0.1443080861705468</v>
+        <v>7.374825364744526</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n">
-        <v>7820</v>
+        <v>6861</v>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>立盈</t>
+          <t>睿生光電</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
         <v/>
       </c>
       <c r="D41" s="2" t="n">
-        <v>455.9291283010479</v>
+        <v>520.3677748667244</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>122</v>
+        <v>194</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
@@ -2619,16 +2619,16 @@
         <v>0</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>59.37629725226439</v>
+        <v>39.38592027300941</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>20.63905468157917</v>
+        <v>25.73460251921511</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>1.17534598729612</v>
+        <v>0.8217212952066411</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" s="2" t="n">
         <v>0</v>
@@ -2637,31 +2637,31 @@
         <v>-1</v>
       </c>
       <c r="N41" s="2" t="n">
-        <v>0.9259724395119142</v>
+        <v>1.952865646932441</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="n">
-        <v>6861</v>
+        <v>7842</v>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>睿生光電</t>
+          <t>天能綠電</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
         <v/>
       </c>
       <c r="D42" s="2" t="n">
-        <v>445.3677748667244</v>
+        <v>512.0029453688378</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>194</v>
+        <v>105</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
@@ -2672,13 +2672,13 @@
         <v>0</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>39.38592026718973</v>
+        <v>59.23997072459637</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>25.73460248263012</v>
+        <v>17.73773654645479</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.8217212952066411</v>
+        <v>0.7238900037053407</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>0</v>
@@ -2690,31 +2690,31 @@
         <v>-1</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>1.952865647123225</v>
+        <v>2.126845414318498</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">
-        <v>6928</v>
+        <v>8021</v>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>攸泰科技</t>
+          <t>尖點</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
         <v/>
       </c>
       <c r="D43" s="2" t="n">
-        <v>444.9986513800548</v>
+        <v>511.2115635424611</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>48.5</v>
+        <v>422.5</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
@@ -2725,16 +2725,16 @@
         <v>0</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>48.59145504282619</v>
+        <v>51.54180543758935</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>12.65737949616135</v>
+        <v>10.8163293181546</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>1.343575451057998</v>
+        <v>1.084422190431448</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" s="2" t="n">
         <v>0</v>
@@ -2743,31 +2743,31 @@
         <v>-1</v>
       </c>
       <c r="N43" s="2" t="n">
-        <v>0.0380244083127796</v>
+        <v>3.953977195133572</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n">
-        <v>7704</v>
+        <v>6862</v>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>明遠精密</t>
+          <t>三集瑞-KY</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
         <v/>
       </c>
       <c r="D44" s="2" t="n">
-        <v>439.1278271309852</v>
+        <v>499.335701207724</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>62.9</v>
+        <v>140.5</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
@@ -2778,16 +2778,16 @@
         <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>56.19721860382292</v>
+        <v>44.44073839154286</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>19.40449437559001</v>
+        <v>16.92747246832571</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>0.3554129558854402</v>
+        <v>1.792675527077364</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L44" s="2" t="n">
         <v>0</v>
@@ -2796,31 +2796,31 @@
         <v>-1</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>-0.1197766276595442</v>
+        <v>1.321245016482967</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>volume_break, market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>7730</v>
+        <v>8034</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>暉盛-創</t>
+          <t>榮群</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>436.7958267093733</v>
+        <v>495.3402839469165</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>185</v>
+        <v>19.9</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,16 +2831,16 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>60.92417768855303</v>
+        <v>58.03099113091995</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>18.55461056539464</v>
+        <v>36.64128466939913</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.279582670937326</v>
+        <v>1.556966515481765</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45" s="2" t="n">
         <v>0</v>
@@ -2849,31 +2849,31 @@
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>3.045062838843982</v>
+        <v>0.22554168357811</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>6916</v>
+        <v>6952</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>華凌</t>
+          <t>大武山</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>435.3331254593085</v>
+        <v>486.5978980949582</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>18.6</v>
+        <v>37.8</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>47.29149443201428</v>
+        <v>56.24754141081061</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>9.102333843044111</v>
+        <v>18.71085199949546</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.220655058630819</v>
+        <v>0.8573716608788876</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>0.0503030933432883</v>
+        <v>-0.0287160096692827</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>6859</v>
+        <v>7828</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>伯特光</t>
+          <t>創新服務</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>432.5389583107344</v>
+        <v>485.0290431584445</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>109</v>
+        <v>1650</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>53.5748711007721</v>
+        <v>49.15604587664177</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>20.7812368313245</v>
+        <v>11.52958303458471</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>1.226124608048363</v>
+        <v>1.292600270824689</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.067181731755054</v>
+        <v>0.3655020401486268</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>6907</v>
+        <v>6863</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>雅特力-KY</t>
+          <t>永道-KY</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>423.5291193161979</v>
+        <v>481.0901713850755</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>186</v>
+        <v>110.5</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,16 +2990,16 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>51.26899115544199</v>
+        <v>45.04017778848711</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>16.3996544301097</v>
+        <v>21.20457751388454</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>0.4336009628028274</v>
+        <v>0.259835428677503</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L48" s="2" t="n">
         <v>0</v>
@@ -3008,31 +3008,31 @@
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>0.1295976839174726</v>
+        <v>-1.583826706587487</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>8021</v>
+        <v>8028</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>尖點</t>
+          <t>昇陽半導體</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>411.2115635424605</v>
+        <v>479.928158668464</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>422.5</v>
+        <v>248.5</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,13 +3043,13 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>51.54180544823903</v>
+        <v>42.24363890295449</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>10.81632936927073</v>
+        <v>21.68354739750306</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.084422190431448</v>
+        <v>0.699188014345717</v>
       </c>
       <c r="K49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>3.953977194589774</v>
+        <v>0.2372379537069626</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>7827</v>
+        <v>6931</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>漢康-KY創</t>
+          <t>青松健康</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>406.5057202764085</v>
+        <v>476.4921460022533</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>162</v>
+        <v>41.5</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>55.52605729686236</v>
+        <v>57.67267185660678</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>12.30020803847714</v>
+        <v>29.13464252976053</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>1.3734750777455</v>
+        <v>0.647291302296907</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.7496852604553994</v>
+        <v>0.1443080861133104</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>7689</v>
+        <v>6914</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>大鵬科CLMX</t>
+          <t>阜爾運通</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>397.7914654640934</v>
+        <v>471.7423680934217</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>176.5</v>
+        <v>125</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>40.05076542146749</v>
+        <v>21.56827928612839</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>23.44947726216694</v>
+        <v>21.76814812691996</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.2316622343443206</v>
+        <v>2.274230864834892</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>3.240207270465336</v>
+        <v>-2.529118198179324</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>7738</v>
+        <v>7827</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>東聯互動</t>
+          <t>漢康-KY創</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>392.7750520530399</v>
+        <v>471.5057202764084</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,16 +3202,16 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>54.68936365009852</v>
+        <v>55.52605732417268</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>33.53764956793049</v>
+        <v>12.30020826346328</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>0.7772390385814227</v>
+        <v>1.3734750777455</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L52" s="2" t="n">
         <v>0</v>
@@ -3220,31 +3220,31 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.3977217251477382</v>
+        <v>0.7496852600356716</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n">
-        <v>6885</v>
+        <v>6928</v>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>全福生技</t>
+          <t>攸泰科技</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
         <v/>
       </c>
       <c r="D53" s="2" t="n">
-        <v>385.4202366196008</v>
+        <v>464.9986513800547</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>22.65</v>
+        <v>48.5</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>0</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>66.36755266056298</v>
+        <v>48.59145504282619</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>20.6719644152353</v>
+        <v>12.65737953435359</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>7.535213916201021</v>
+        <v>1.343575451057998</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L53" s="2" t="n">
         <v>0</v>
@@ -3273,31 +3273,31 @@
         <v>-1</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>0.2685360860457264</v>
+        <v>0.038024408112447</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n">
-        <v>6921</v>
+        <v>6909</v>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>嘉雨思-創</t>
+          <t>創控</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
         <v/>
       </c>
       <c r="D54" s="2" t="n">
-        <v>384.2573828405479</v>
+        <v>459.2985793675997</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>67.40000000000001</v>
+        <v>41.55</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
@@ -3308,16 +3308,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>50.90262127056939</v>
+        <v>48.3194208690425</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>16.48629218411205</v>
+        <v>19.56320945178108</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>0.2934450157328424</v>
+        <v>1.12154520476031</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L54" s="2" t="n">
         <v>0</v>
@@ -3326,31 +3326,31 @@
         <v>-1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>0.0485361868160284</v>
+        <v>0.4533243511106581</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n">
-        <v>7768</v>
+        <v>7820</v>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>頌勝科技</t>
+          <t>立盈</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
         <v/>
       </c>
       <c r="D55" s="2" t="n">
-        <v>382.5212339461172</v>
+        <v>455.9291283010478</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>290</v>
+        <v>122</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
@@ -3361,13 +3361,13 @@
         <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>51.41326113058712</v>
+        <v>59.37629723965183</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>27.55852559889561</v>
+        <v>20.63905471357462</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>0.5309062468348422</v>
+        <v>1.17534598729612</v>
       </c>
       <c r="K55" s="2" t="n">
         <v>0</v>
@@ -3379,31 +3379,31 @@
         <v>-1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>5.310227539077473</v>
+        <v>0.9259724389395338</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="n">
-        <v>6952</v>
+        <v>7610</v>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>大武山</t>
+          <t>聯友金屬-創</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
         <v/>
       </c>
       <c r="D56" s="2" t="n">
-        <v>376.5978980949577</v>
+        <v>445.783774475027</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>37.8</v>
+        <v>1595</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
@@ -3414,13 +3414,13 @@
         <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>56.24754143742322</v>
+        <v>44.4920923937453</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>18.71085193646908</v>
+        <v>13.96265633384465</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>0.8573716608788876</v>
+        <v>0.8642401565758795</v>
       </c>
       <c r="K56" s="2" t="n">
         <v>0</v>
@@ -3432,31 +3432,31 @@
         <v>-1</v>
       </c>
       <c r="N56" s="2" t="n">
-        <v>-0.0287160097646811</v>
+        <v>-0.1791350479156293</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>6923</v>
+        <v>6951</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>中台</t>
+          <t>青新-創</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>375.7046931241217</v>
+        <v>443.9689552992222</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,16 +3467,16 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>53.57365132152146</v>
+        <v>43.7197870985456</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>8.577772577728323</v>
+        <v>26.74505730413168</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.9705190843697832</v>
+        <v>0.082506877674476</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L57" s="2" t="n">
         <v>0</v>
@@ -3485,31 +3485,31 @@
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>0.1830175959883124</v>
+        <v>0.2167519938326214</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>7842</v>
+        <v>6890</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>天能綠電</t>
+          <t>來億-KY</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>372.0029453688379</v>
+        <v>443.8751921177249</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>105</v>
+        <v>173.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,16 +3520,16 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>59.23997058686356</v>
+        <v>51.09359507252905</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>17.73773650962456</v>
+        <v>14.01002472126296</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>0.7238900037053407</v>
+        <v>2.191174035993523</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L58" s="2" t="n">
         <v>0</v>
@@ -3538,31 +3538,31 @@
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>2.126845415081678</v>
+        <v>1.608608159459288</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, liquidity_ok, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>6863</v>
+        <v>7769</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>永道-KY</t>
+          <t>鴻勁</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>371.0901713850755</v>
+        <v>442.4053870552785</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>110.5</v>
+        <v>6345</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>45.0401777970722</v>
+        <v>48.91823426659774</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>21.20457750974832</v>
+        <v>8.096417538138184</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.259835428677503</v>
+        <v>0.7560541867330458</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L59" s="2" t="n">
         <v>0</v>
@@ -3591,31 +3591,31 @@
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>-1.583826705538119</v>
+        <v>-10.10242264751225</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>7728</v>
+        <v>6873</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>光焱科技</t>
+          <t>泓德能源</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>368.4419931705929</v>
+        <v>440.8489501930347</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>630</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>56.46513630755169</v>
+        <v>38.39512980942256</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>19.78578896567046</v>
+        <v>26.48304673483787</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>1.794991558806978</v>
+        <v>0.4880018373466401</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L60" s="2" t="n">
         <v>0</v>
@@ -3644,31 +3644,31 @@
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>7.374825366557024</v>
+        <v>0.0526065104654267</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n">
-        <v>6924</v>
+        <v>7704</v>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>榮惠-KY創</t>
+          <t>明遠精密</t>
         </is>
       </c>
       <c r="C61" s="2" t="n">
         <v/>
       </c>
       <c r="D61" s="2" t="n">
-        <v>366.0478615350394</v>
+        <v>439.1278271309852</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>115.5</v>
+        <v>62.9</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>52.46233946049008</v>
+        <v>56.19721855871415</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15.82987138162742</v>
+        <v>19.40449438605337</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>1.466602275814192</v>
+        <v>0.3554129558854402</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L61" s="2" t="n">
         <v>0</v>
@@ -3697,31 +3697,31 @@
         <v>-1</v>
       </c>
       <c r="N61" s="2" t="n">
-        <v>0.3824736613574586</v>
+        <v>-0.11977662767863</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery</t>
+          <t>ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>7855</v>
+        <v>6916</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>和運租車</t>
+          <t>華凌</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>363.2224421720978</v>
+        <v>435.3331254593085</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>43.45</v>
+        <v>18.6</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>18.13493043610525</v>
+        <v>47.29149446625079</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>44.61787360987765</v>
+        <v>9.102333997363807</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.4328635889170414</v>
+        <v>1.220655058630819</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>0</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>-0.0236175447067505</v>
+        <v>0.0503030932574311</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>6895</v>
+        <v>6859</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>宏碩系統</t>
+          <t>伯特光</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>362.8580704829863</v>
+        <v>432.5389583107344</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>147</v>
+        <v>109</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,13 +3785,13 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>71.43855208495275</v>
+        <v>53.57487113950602</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>21.98057704011988</v>
+        <v>20.7812368313245</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.180150374796492</v>
+        <v>1.226124608048363</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>3.935081456752232</v>
+        <v>1.067181731087269</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, breakout_20d, market_above_ma60, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>6962</v>
+        <v>6994</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>奕力-KY</t>
+          <t>富威電力</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>359.2429274386913</v>
+        <v>431.5795428073905</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>31.35</v>
+        <v>36.5</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>45.10485108142796</v>
+        <v>42.20660241890605</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>19.16371131655314</v>
+        <v>31.45133825863028</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.8966367417322313</v>
+        <v>0.5636316040713879</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>0.1382075369345109</v>
+        <v>0.5005398809237074</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>6870</v>
+        <v>6958</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>騰雲</t>
+          <t>日盛台駿</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>358.5527557905228</v>
+        <v>423.8384087457396</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>253.5</v>
+        <v>17.7</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>44.61036489587084</v>
+        <v>48.85052816355367</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>9.106883325536414</v>
+        <v>19.33712895306046</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.257544653040175</v>
+        <v>0.3661087654283487</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.6117729778744048</v>
+        <v>-0.0225693524753023</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>6996</v>
+        <v>6907</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>力領科技</t>
+          <t>雅特力-KY</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>354.9303501850489</v>
+        <v>423.5291193161979</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>181.5</v>
+        <v>186</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>53.06498695109965</v>
+        <v>51.26899115544199</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>13.60549889021387</v>
+        <v>16.3996544301097</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.5910807844792678</v>
+        <v>0.4336009628028274</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>0.7405420391690343</v>
+        <v>0.1295976839174726</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>6902</v>
+        <v>8040</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>GOGOLOOK</t>
+          <t>九暘</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>351.3651877611201</v>
+        <v>416.0948682137564</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>127</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>50.28650417008048</v>
+        <v>44.41448370949562</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>13.61879096490591</v>
+        <v>21.50508826291989</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.5211181333614584</v>
+        <v>0.6824378849469815</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>-0.1464779468953938</v>
+        <v>0.743958236336737</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>7791</v>
+        <v>7749</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>皇家可口</t>
+          <t>意騰-KY</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>351.2085367530684</v>
+        <v>407.09883162951</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>57.1</v>
+        <v>373</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,13 +4050,13 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>32.45650872201588</v>
+        <v>54.51936367091493</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>38.2160819583293</v>
+        <v>22.71816336674541</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>0.2770231521518799</v>
+        <v>1.247540426445335</v>
       </c>
       <c r="K68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.0337548829888691</v>
+        <v>7.047840556815474</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>6855</v>
+        <v>6921</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>數泓科</t>
+          <t>嘉雨思-創</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>350.1566897487328</v>
+        <v>404.2573828405479</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>0</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,16 +4103,16 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>41.69656358293148</v>
+        <v>50.90262127056939</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>11.63342436520135</v>
+        <v>16.48629218411205</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>0.009931765095363299</v>
+        <v>0.2934450157328424</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>-4.270767300814836</v>
+        <v>0.0485361868160284</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>6903</v>
+        <v>7689</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>巨漢</t>
+          <t>大鵬科CLMX</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>350.1451678966371</v>
+        <v>397.7914654640934</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>314</v>
+        <v>176.5</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>44.43809058940051</v>
+        <v>40.05076542146749</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>18.03700840075789</v>
+        <v>23.44947726216694</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.4999583828905491</v>
+        <v>0.2316622343443206</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>1.853845110390765</v>
+        <v>3.240207270465336</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>6873</v>
+        <v>7705</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>泓德能源</t>
+          <t>三商餐飲</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>345.8489501930349</v>
+        <v>396.0293388504877</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>69.90000000000001</v>
+        <v>30.9</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>38.39512956999748</v>
+        <v>51.83576760480567</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>26.48304678386611</v>
+        <v>22.69006117086723</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>0.4880018373466401</v>
+        <v>0.8653093400021746</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.0526065116101945</v>
+        <v>0.0498412796379264</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>7823</v>
+        <v>6923</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>奧義賽博-KY創</t>
+          <t>中台</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>340.054227491323</v>
+        <v>395.7046931241213</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>83.5</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>50.00591239768787</v>
+        <v>53.57365159871895</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>21.83017959430967</v>
+        <v>8.577772704981111</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.9979076561069036</v>
+        <v>0.9705190843697832</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.0469597683197477</v>
+        <v>0.1830175950534123</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>6951</v>
+        <v>7721</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>青新-創</t>
+          <t>微程式</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>333.9689552992222</v>
+        <v>393.5223110497212</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>62</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>43.71978680754497</v>
+        <v>46.21429954905033</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>26.74505710876726</v>
+        <v>16.76795596821339</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.082506877674476</v>
+        <v>0.6888779970105845</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>0.2167519942142144</v>
+        <v>0.3107235956628502</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>8011</v>
+        <v>7738</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>台通</t>
+          <t>東聯互動</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>330.8596452445902</v>
+        <v>392.7750520530399</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>16.1</v>
+        <v>170</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>45.95351698896016</v>
+        <v>54.68936365009852</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>30.15511431764322</v>
+        <v>33.5376495940386</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.7085885245198115</v>
+        <v>0.7772390385814227</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,7 +4386,7 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>0.0436944950054569</v>
+        <v>0.3977217247661617</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4396,21 +4396,21 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>7610</v>
+        <v>7768</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>聯友金屬-創</t>
+          <t>頌勝科技</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>330.7837744750267</v>
+        <v>382.5212339461173</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>1595</v>
+        <v>290</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>44.49209239368572</v>
+        <v>51.41326113058712</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>13.96265633182071</v>
+        <v>27.55852561386708</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.8642401565758795</v>
+        <v>0.5309062468348422</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.1791350480111759</v>
+        <v>5.310227539459029</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>7818</v>
+        <v>6902</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>溢泰實業</t>
+          <t>GOGOLOOK</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>327.8392682096937</v>
+        <v>371.3651877611201</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>61</v>
+        <v>127</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>32.06800924794389</v>
+        <v>50.28650431812325</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>19.90882102894545</v>
+        <v>13.61879098302197</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>0.7001859245535994</v>
+        <v>0.5211181333614584</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>0.0489486890261636</v>
+        <v>-0.1464779475250134</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>8034</v>
+        <v>7791</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>榮群</t>
+          <t>皇家可口</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>325.3402839469165</v>
+        <v>371.2085367530685</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>19.9</v>
+        <v>57.1</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>58.0309912018893</v>
+        <v>32.45650928826996</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>36.64128466939912</v>
+        <v>38.21608205307732</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>1.556966515481765</v>
+        <v>0.2770231521518799</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>0.2255416836353481</v>
+        <v>0.0337548829697929</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>volume_break, rsi_strong, market_above_ma60, adx_trending, mfi_strong</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>7805</v>
+        <v>6924</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>威聯通</t>
+          <t>榮惠-KY創</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>324.1624590533248</v>
+        <v>366.0478615350394</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>510</v>
+        <v>115.5</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>26.30966956021916</v>
+        <v>52.4623394700894</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>34.79162731156539</v>
+        <v>15.82987138302226</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.3840896319190784</v>
+        <v>1.466602275814192</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-19.78368561140612</v>
+        <v>0.3824736607659951</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, kd_golden_cross, williams_r_recovery</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>6901</v>
+        <v>7855</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>鑽石投資</t>
+          <t>和運租車</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>317.8325792738765</v>
+        <v>363.2224421720978</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>16.55</v>
+        <v>43.45</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>46.93423424638308</v>
+        <v>18.13493043610525</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>11.30575722803371</v>
+        <v>44.61787360987765</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>0.5531716023259418</v>
+        <v>0.4328635889170414</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>-0.0142899842368916</v>
+        <v>-0.0236175447067505</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>6994</v>
+        <v>6908</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>富威電力</t>
+          <t>宏碁遊戲-創</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>316.5795428073905</v>
+        <v>359.779855796087</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>36.5</v>
+        <v>30.6</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>42.20660221670869</v>
+        <v>32.93763059821183</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>31.45133825915029</v>
+        <v>35.23689551106127</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>0.5636316040713879</v>
+        <v>1.243265595463138</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>0.500539881686892</v>
+        <v>-0.0236158008882181</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>7734</v>
+        <v>6962</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>印能科技</t>
+          <t>奕力-KY</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>315.0546487869052</v>
+        <v>359.2429274386913</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>2870</v>
+        <v>31.35</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,13 +4739,13 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>43.31950384756068</v>
+        <v>45.10485117284883</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>15.39180795249394</v>
+        <v>19.16371128876165</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>1.630127986544363</v>
+        <v>0.8966367417322313</v>
       </c>
       <c r="K81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>-31.79647746538524</v>
+        <v>0.1382075365338431</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>6958</v>
+        <v>6870</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>日盛台駿</t>
+          <t>騰雲</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>313.8384087457396</v>
+        <v>358.5527557905228</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>17.7</v>
+        <v>253.5</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,13 +4792,13 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>48.85052811518729</v>
+        <v>44.61036487301062</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>19.33712888256688</v>
+        <v>9.106883351257956</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>0.3661087654283487</v>
+        <v>1.257544653040175</v>
       </c>
       <c r="K82" s="2" t="n">
         <v>0</v>
@@ -4810,7 +4810,7 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>-0.0225693524085254</v>
+        <v>0.6117729772066065</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
@@ -4820,21 +4820,21 @@
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>6944</v>
+        <v>6996</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>兆聯實業</t>
+          <t>力領科技</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>312.779588680361</v>
+        <v>354.9303501850491</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>716</v>
+        <v>181.5</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,13 +4845,13 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>38.94540455722628</v>
+        <v>53.06498697049799</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>26.39823173852452</v>
+        <v>13.60549900724691</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.6409035504573405</v>
+        <v>0.5910807844792678</v>
       </c>
       <c r="K83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>4.981702807919078</v>
+        <v>0.7405420385966361</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>7760</v>
+        <v>8011</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>享溫馨</t>
+          <t>台通</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>309.9234623754999</v>
+        <v>350.8596452445901</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>33.3</v>
+        <v>16.1</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>48.74737493718645</v>
+        <v>45.9535170384331</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>8.321480595647655</v>
+        <v>30.15511434930737</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.891037128028912</v>
+        <v>0.7085885245198115</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>0.0422280234663161</v>
+        <v>0.0436944949195963</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>7703</v>
+        <v>6855</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>銳澤</t>
+          <t>數泓科</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>307.6770386045513</v>
+        <v>350.1566897487328</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>182</v>
+        <v>0</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,13 +4951,13 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>51.74737540989212</v>
+        <v>41.69656358293148</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>11.09853985164018</v>
+        <v>11.6334245572231</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.4081835268392055</v>
+        <v>0.009931765095363299</v>
       </c>
       <c r="K85" s="2" t="n">
         <v>0</v>
@@ -4969,7 +4969,7 @@
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>1.300115228301086</v>
+        <v>-4.270767300910226</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
@@ -4979,21 +4979,21 @@
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>8040</v>
+        <v>6903</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>九暘</t>
+          <t>巨漢</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>301.0948682137563</v>
+        <v>350.1451678966371</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>71.59999999999999</v>
+        <v>314</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,13 +5004,13 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.41448370704352</v>
+        <v>44.43809058338474</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>21.50508822653944</v>
+        <v>18.03700846225769</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.6824378849469815</v>
+        <v>0.4999583828905491</v>
       </c>
       <c r="K86" s="2" t="n">
         <v>2</v>
@@ -5022,31 +5022,31 @@
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>0.7439582364512169</v>
+        <v>1.853845110009194</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>7765</v>
+        <v>7823</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>中華資安</t>
+          <t>奧義賽博-KY創</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>293.8698558900923</v>
+        <v>340.054227491323</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>225.5</v>
+        <v>83.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>50.65433089485846</v>
+        <v>50.00591239768787</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>19.73048646654296</v>
+        <v>21.83017959430967</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.7786459123364894</v>
+        <v>0.9979076561069036</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>0.2075637606136665</v>
+        <v>-0.0469597683197477</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>6925</v>
+        <v>7818</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>意藍</t>
+          <t>溢泰實業</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>293.151474038337</v>
+        <v>327.8392682096937</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>50.3</v>
+        <v>61</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,16 +5110,16 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>36.51471258107586</v>
+        <v>32.06800944985974</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>13.54564461474886</v>
+        <v>19.90882110773805</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5223679638637942</v>
+        <v>0.7001859245535994</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L88" s="2" t="n">
         <v>0</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>0.0904702147202647</v>
+        <v>0.0489486885300975</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>7705</v>
+        <v>7805</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>三商餐飲</t>
+          <t>威聯通</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>286.029338850488</v>
+        <v>324.1624590533248</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>30.9</v>
+        <v>510</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,13 +5163,13 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>51.83576731530561</v>
+        <v>26.309669679549</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>22.69006115839763</v>
+        <v>34.79162731982124</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8653093400021746</v>
+        <v>0.3840896319190784</v>
       </c>
       <c r="K89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>0.0498412797905611</v>
+        <v>-19.78368561331403</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>6890</v>
+        <v>7722</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>來億-KY</t>
+          <t>LINEPAY</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>283.8751921177249</v>
+        <v>318.3898451183479</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>173.5</v>
+        <v>288</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,16 +5216,16 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>51.0935948378234</v>
+        <v>51.07685639965766</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>14.01002473839252</v>
+        <v>13.35991161371745</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>2.191174035993523</v>
+        <v>0.6053924477483407</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L90" s="2" t="n">
         <v>0</v>
@@ -5234,31 +5234,31 @@
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>1.608608163752174</v>
+        <v>1.749583315927374</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>7721</v>
+        <v>6901</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>微程式</t>
+          <t>鑽石投資</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>283.5223110497212</v>
+        <v>317.8325792738765</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>62</v>
+        <v>16.55</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>46.21429933804461</v>
+        <v>46.93423428374481</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>16.76795588075265</v>
+        <v>11.30575723819538</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.6888779970105845</v>
+        <v>0.5531716023259418</v>
       </c>
       <c r="K91" s="2" t="n">
         <v>0</v>
@@ -5287,31 +5287,31 @@
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>0.3107235963306318</v>
+        <v>-0.0142899843513681</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>6862</v>
+        <v>7734</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>三集瑞-KY</t>
+          <t>印能科技</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>274.335701207724</v>
+        <v>315.0546487869063</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>140.5</v>
+        <v>2870</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,13 +5322,13 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>44.44073834054867</v>
+        <v>43.31950385427514</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>16.92747245900755</v>
+        <v>15.39180797749882</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.792675527077364</v>
+        <v>1.630127986544363</v>
       </c>
       <c r="K92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>1.321245017055348</v>
+        <v>-31.79647746920112</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>6919</v>
+        <v>6944</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>康霈*</t>
+          <t>兆聯實業</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>264.508692689518</v>
+        <v>313.8911103065096</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>103</v>
+        <v>716</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,13 +5375,13 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>46.34247243185008</v>
+        <v>38.94540458311134</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>16.1442806716391</v>
+        <v>26.39823181860304</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.092332758604334</v>
+        <v>0.781966116297815</v>
       </c>
       <c r="K93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>-0.335263808922186</v>
+        <v>4.981702805534155</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>6967</v>
+        <v>7765</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>汎瑋材料</t>
+          <t>中華資安</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>262.1084543879265</v>
+        <v>313.8698558900923</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>225.5</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.47519330979237</v>
+        <v>50.65433083400527</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>9.154953916611928</v>
+        <v>19.73048646654296</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.6908998684074409</v>
+        <v>0.7786459123364894</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.2485656207444252</v>
+        <v>0.2075637605182528</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>6877</v>
+        <v>7760</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>鏵友益</t>
+          <t>享溫馨</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>261.4521535592545</v>
+        <v>309.9234623754999</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>116</v>
+        <v>33.3</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>42.75217508750718</v>
+        <v>48.74737491742325</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>19.46083611980782</v>
+        <v>8.321481109822317</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.287361977414915</v>
+        <v>1.891037128028912</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.3100802991237539</v>
+        <v>0.0422280235712441</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>7769</v>
+        <v>7703</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>鴻勁</t>
+          <t>銳澤</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>257.4053870552785</v>
+        <v>307.6770386045514</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>6345</v>
+        <v>182</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>48.91823423363647</v>
+        <v>51.74737553910301</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>8.096417391251725</v>
+        <v>11.09853985164018</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.7560541867330458</v>
+        <v>0.4081835268392055</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>-10.10242263415683</v>
+        <v>1.30011522772869</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>7770</v>
+        <v>8038</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>君曜</t>
+          <t>長園科</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>252.6754741190877</v>
+        <v>301.777821709517</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>36.95</v>
+        <v>32</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,16 +5587,16 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.14825956210115</v>
+        <v>44.24591556795584</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>6.238885407877797</v>
+        <v>24.34076243094775</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>2.698972609340966</v>
+        <v>1.423023383545979</v>
       </c>
       <c r="K97" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>0.2572455215350687</v>
+        <v>0.3185587347467511</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>6865</v>
+        <v>6925</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>偉康科技</t>
+          <t>意藍</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>251.1614127818485</v>
+        <v>293.151474038337</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>26</v>
+        <v>50.3</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>53.75265945239134</v>
+        <v>36.51471355657267</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>11.25735263107512</v>
+        <v>13.54564443911041</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.460754825079672</v>
+        <v>0.5223679638637942</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>1.210789521543283</v>
+        <v>0.0904702132893091</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>6908</v>
+        <v>6919</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>宏碁遊戲-創</t>
+          <t>康霈*</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>249.7798557960869</v>
+        <v>264.508692689518</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>30.6</v>
+        <v>103</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,13 +5693,13 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>32.93763070417729</v>
+        <v>46.34247067868248</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>35.23689556013179</v>
+        <v>16.14428066188511</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>1.243265595463138</v>
+        <v>1.092332758604334</v>
       </c>
       <c r="K99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>-0.0236158008882181</v>
+        <v>-0.3352638103238735</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>6997</v>
+        <v>6967</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>博弘</t>
+          <t>汎瑋材料</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>242.5519175292307</v>
+        <v>262.1084543879269</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>68</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,13 +5746,13 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>52.26043999979121</v>
+        <v>52.47519327393022</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>8.659303628251104</v>
+        <v>9.15495387120246</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.761141204379099</v>
+        <v>0.6908998684074409</v>
       </c>
       <c r="K100" s="2" t="n">
         <v>0</v>
@@ -5764,31 +5764,31 @@
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>3.812740341209309</v>
+        <v>0.248565621087859</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>7839</v>
+        <v>6877</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>達人網</t>
+          <t>鏵友益</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>240.4519000987058</v>
+        <v>261.4521535592544</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>45</v>
+        <v>116</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>45.80647484277896</v>
+        <v>42.75217508167889</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>27.14370723105605</v>
+        <v>19.46083614300946</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.7515580295555926</v>
+        <v>0.287361977414915</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.0358630307334961</v>
+        <v>-0.310080299581664</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>6971</v>
+        <v>7770</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>惠民實業</t>
+          <t>君曜</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>239.2982486819645</v>
+        <v>252.6754741190877</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>26.3</v>
+        <v>36.95</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,16 +5852,16 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>53.29572617440049</v>
+        <v>50.14825963253168</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.49234826340258</v>
+        <v>6.238885292203726</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>1.16637446078555</v>
+        <v>2.698972609340966</v>
       </c>
       <c r="K102" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L102" s="2" t="n">
         <v>0</v>
@@ -5870,31 +5870,31 @@
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>0.1370324258924646</v>
+        <v>0.2572455209817592</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>7749</v>
+        <v>6865</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>意騰-KY</t>
+          <t>偉康科技</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>237.09883162951</v>
+        <v>251.1614127818485</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>373</v>
+        <v>26</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,13 +5905,13 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>54.51936369420969</v>
+        <v>53.75265946037592</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>22.71816341747344</v>
+        <v>11.2573526333702</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.247540426445335</v>
+        <v>0.460754825079672</v>
       </c>
       <c r="K103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>7.047840561966931</v>
+        <v>1.210789521390646</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>6909</v>
+        <v>6997</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>創控</t>
+          <t>博弘</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>234.2985793675997</v>
+        <v>242.5519175292307</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>41.55</v>
+        <v>68</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,13 +5958,13 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>48.31942084273181</v>
+        <v>52.2604400022213</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>19.56320942179937</v>
+        <v>8.659303628159599</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>1.12154520476031</v>
+        <v>0.761141204379099</v>
       </c>
       <c r="K104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>0.4533243513014555</v>
+        <v>3.812740341018518</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>6955</v>
+        <v>7839</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>邦睿生技-創</t>
+          <t>達人網</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>221.7047945748112</v>
+        <v>240.4519000987058</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>108</v>
+        <v>45</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,13 +6011,13 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>48.90888803131103</v>
+        <v>45.80647559996981</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>6.978198396816104</v>
+        <v>27.14370735359268</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>1.286702514027758</v>
+        <v>0.7515580295555926</v>
       </c>
       <c r="K105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.4174613262713906</v>
+        <v>0.0358630307334961</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>6899</v>
+        <v>6971</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>創為精密</t>
+          <t>惠民實業</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>219.1665503017845</v>
+        <v>239.2982486819644</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>50.2</v>
+        <v>26.3</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>39.77194906753353</v>
+        <v>53.29572643206797</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>20.35002481815085</v>
+        <v>16.4923482967899</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.9560668279237216</v>
+        <v>1.16637446078555</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.197040989838507</v>
+        <v>0.1370324257398293</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>8032</v>
+        <v>6965</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>光菱</t>
+          <t>中傑-KY</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>218.0141079962234</v>
+        <v>227.1254990241676</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>36.3</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,16 +6117,16 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>45.83844223366474</v>
+        <v>44.02514810295438</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>21.03300383477334</v>
+        <v>34.57725812484002</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>0.4995383681460357</v>
+        <v>0.790578711928077</v>
       </c>
       <c r="K107" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L107" s="2" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>0.1800873103934004</v>
+        <v>0.0666446930063892</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
@@ -6145,21 +6145,21 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>7722</v>
+        <v>6955</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>LINEPAY</t>
+          <t>邦睿生技-創</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>208.389845118348</v>
+        <v>221.7047945748112</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>288</v>
+        <v>108</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>51.0768565847912</v>
+        <v>48.90888742708118</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>13.3599115818323</v>
+        <v>6.978198398328974</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>0.6053924477483407</v>
+        <v>1.286702514027758</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>1.749583317072123</v>
+        <v>0.417461326080584</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>6965</v>
+        <v>6899</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>中傑-KY</t>
+          <t>創為精密</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>207.1254990241663</v>
+        <v>219.1665503017845</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>75.09999999999999</v>
+        <v>50.2</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,13 +6223,13 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>44.02514781675749</v>
+        <v>39.77194909016787</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>34.57725816444639</v>
+        <v>20.35002481815085</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>0.790578711928077</v>
+        <v>0.9560668279237216</v>
       </c>
       <c r="K109" s="2" t="n">
         <v>0</v>
@@ -6241,7 +6241,7 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>0.06664469384587821</v>
+        <v>0.1970409896477025</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
@@ -6251,21 +6251,21 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>8024</v>
+        <v>8032</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>佑華</t>
+          <t>光菱</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>198.2111892730679</v>
+        <v>218.0141079962233</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>13.2</v>
+        <v>36.3</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,13 +6276,13 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>38.69017462890231</v>
+        <v>45.83844225174059</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>13.05614945252112</v>
+        <v>21.03300394685732</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.9332964454026824</v>
+        <v>0.4995383681460357</v>
       </c>
       <c r="K110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.0327795049547725</v>
+        <v>0.1800873102026072</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>6894</v>
+        <v>7736</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>衛司特</t>
+          <t>虎山</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>195.1071622803757</v>
+        <v>202.8258240452267</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>330</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>46.618408904058</v>
+        <v>42.78114845523294</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>8.639439670630686</v>
+        <v>12.96256493585254</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.8419055404590514</v>
+        <v>0.6993509066300061</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.4667868365851402</v>
+        <v>-0.06832609434848309</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>7736</v>
+        <v>8024</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>虎山</t>
+          <t>佑華</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>182.8258240452267</v>
+        <v>198.2111892730679</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>69.09999999999999</v>
+        <v>13.2</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,13 +6382,13 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>42.78114858730506</v>
+        <v>38.69017460414101</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>12.96256493585254</v>
+        <v>13.05614943915056</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.6993509066300061</v>
+        <v>0.9332964454026824</v>
       </c>
       <c r="K112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>-0.06832609444387761</v>
+        <v>-0.0327795049643119</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>6910</v>
+        <v>6894</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>德鴻</t>
+          <t>衛司特</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>173.9290574567661</v>
+        <v>195.1071622803757</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>24.5</v>
+        <v>330</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>44.43734719702884</v>
+        <v>46.618408904058</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>17.27110358255211</v>
+        <v>8.639439721568422</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.3257358972762393</v>
+        <v>0.8419055404590514</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>0.0861850262359629</v>
+        <v>-0.4667868368713672</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>7715</v>
+        <v>6854</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>裕山</t>
+          <t>錼創科技-KY創</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>171.6820479497884</v>
+        <v>191.6523510096272</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>30.4</v>
+        <v>93.7</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,13 +6488,13 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>41.00581701856783</v>
+        <v>44.99480595223589</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>16.34799539245808</v>
+        <v>28.19317031157492</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>1.124428090497928</v>
+        <v>0.6911233900573404</v>
       </c>
       <c r="K114" s="2" t="n">
         <v>2</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.245947233385097</v>
+        <v>1.080882538188284</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>6854</v>
+        <v>7803</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>錼創科技-KY創</t>
+          <t>雲象科技-創</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>171.6523510096272</v>
+        <v>187.1415050389879</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>93.7</v>
+        <v>19.15</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>44.99480616453484</v>
+        <v>38.22838049163709</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>28.19317027147444</v>
+        <v>14.31500038252407</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.6911233900573404</v>
+        <v>0.4949279593332331</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>1.080882538188284</v>
+        <v>0.1008415749594777</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>7803</v>
+        <v>6869</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>雲象科技-創</t>
+          <t>雲豹能源</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>167.1415050389879</v>
+        <v>175.8792538393981</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>19.15</v>
+        <v>67.8</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>38.22838069931983</v>
+        <v>49.79769720835415</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>14.31500051438262</v>
+        <v>16.06937835025753</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.4949279593332331</v>
+        <v>0.3723114470895552</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>0.1008415748926983</v>
+        <v>0.3948658343026605</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>7821</v>
+        <v>6910</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>神數</t>
+          <t>德鴻</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>165.5274005188668</v>
+        <v>173.9290574567645</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>38.85</v>
+        <v>24.5</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,13 +6647,13 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>39.47864797387265</v>
+        <v>44.43734653409631</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>14.60163637430399</v>
+        <v>17.27110359939715</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.8374226932941961</v>
+        <v>0.3257358972762393</v>
       </c>
       <c r="K117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>0.0265322963460425</v>
+        <v>0.0861850264458378</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>8038</v>
+        <v>7715</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>長園科</t>
+          <t>裕山</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>161.7778217095169</v>
+        <v>171.6820479497884</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>32</v>
+        <v>30.4</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>44.24591545878953</v>
+        <v>41.00581702685442</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>24.34076238399094</v>
+        <v>16.34799538670753</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.423023383545979</v>
+        <v>1.124428090497928</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>0.3185587352142023</v>
+        <v>-0.2459472334327954</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>7547</v>
+        <v>7821</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>碩網</t>
+          <t>神數</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>154.5980089120124</v>
+        <v>165.5274005188674</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>50.6</v>
+        <v>38.85</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>42.92313686899436</v>
+        <v>39.47864799442011</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>14.93077102347462</v>
+        <v>14.60163642144645</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.7027988722356036</v>
+        <v>0.8374226932941961</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>0</v>
@@ -6771,7 +6771,7 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-0.0230559736885722</v>
+        <v>0.0265322961361731</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
@@ -6781,21 +6781,21 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>6934</v>
+        <v>7547</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>心誠鎂</t>
+          <t>碩網</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>149.4353868677416</v>
+        <v>154.5980089120169</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>72.40000000000001</v>
+        <v>50.6</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,13 +6806,13 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>45.75827615622641</v>
+        <v>42.92313605680936</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>14.69536468391378</v>
+        <v>14.93077144001108</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>0.4928999307364289</v>
+        <v>0.7027988722356036</v>
       </c>
       <c r="K120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>0.08665821355883389</v>
+        <v>-0.0230559719714206</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>7786</v>
+        <v>6934</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>東方風能</t>
+          <t>心誠鎂</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>147.8194113879361</v>
+        <v>149.4353868677416</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>119</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,13 +6859,13 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>38.41008839803534</v>
+        <v>45.75827624813624</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>11.10872462185132</v>
+        <v>14.69536445969483</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.731519174357545</v>
+        <v>0.4928999307364289</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.668224021931993</v>
+        <v>0.0866582133680497</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>6947</v>
+        <v>7786</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>台鎔科技</t>
+          <t>東方風能</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>142.2908886499988</v>
+        <v>147.8194113879368</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>70.3</v>
+        <v>119</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>37.43672973871841</v>
+        <v>38.41008841516518</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>14.89343708764405</v>
+        <v>11.1087247084943</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.5891281667532151</v>
+        <v>0.731519174357545</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,7 +6930,7 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-0.080037576041045</v>
+        <v>-0.6682240218366127</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
@@ -6940,21 +6940,21 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>7772</v>
+        <v>6947</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>耀穎</t>
+          <t>台鎔科技</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>136.8385367092885</v>
+        <v>142.2908886499988</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>89</v>
+        <v>70.3</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,16 +6965,16 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>41.93735960439616</v>
+        <v>37.43672973594425</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>18.7556721534676</v>
+        <v>14.89343708764405</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>0.7721425550526556</v>
+        <v>0.5891281667532151</v>
       </c>
       <c r="K123" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L123" s="2" t="n">
         <v>0</v>
@@ -6983,7 +6983,7 @@
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>1.193075969373031</v>
+        <v>-0.0800375760601226</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
@@ -6993,21 +6993,21 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>7732</v>
+        <v>7772</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>金興精密</t>
+          <t>耀穎</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>131.8369176400604</v>
+        <v>136.8385367092885</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>34.7</v>
+        <v>89</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,13 +7018,13 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>50.26198241239644</v>
+        <v>41.93735990914805</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>3.885702330920369</v>
+        <v>18.75567217655256</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.1150893668933927</v>
+        <v>0.7721425550526556</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
@@ -7036,31 +7036,31 @@
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0574039263244447</v>
+        <v>1.193075967178897</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>7740</v>
+        <v>7732</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>熙特爾-創</t>
+          <t>金興精密</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>126.83589525229</v>
+        <v>131.8369176400604</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>136.5</v>
+        <v>34.7</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,13 +7071,13 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>41.00936328974242</v>
+        <v>50.26198033984387</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>11.99075273956122</v>
+        <v>3.885702435978969</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>0.4067036707927562</v>
+        <v>0.1150893668933927</v>
       </c>
       <c r="K125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-1.133168653391033</v>
+        <v>-0.0574039263244447</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>7747</v>
+        <v>7740</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>昕奇雲端</t>
+          <t>熙特爾-創</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>125.0043252021095</v>
+        <v>126.8358952522899</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>114</v>
+        <v>136.5</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,13 +7124,13 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>52.12970268845516</v>
+        <v>41.00936309118309</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>9.912568762119388</v>
+        <v>11.9907527704419</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>0.4004325202109512</v>
+        <v>0.4067036707927562</v>
       </c>
       <c r="K126" s="2" t="n">
         <v>0</v>
@@ -7142,7 +7142,7 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>4.892111111124676</v>
+        <v>-1.133168651006118</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
@@ -7152,21 +7152,21 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>7753</v>
+        <v>7747</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>星亞</t>
+          <t>昕奇雲端</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>70.89062056325089</v>
+        <v>125.0043252021095</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>37.2</v>
+        <v>114</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>40.3751953236749</v>
+        <v>52.12970268075351</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>7.754069261848413</v>
+        <v>9.912569026957469</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.6812575911705968</v>
+        <v>0.4004325202109512</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,7 +7195,7 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>0.12056230864653</v>
+        <v>4.892111110933877</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
@@ -7205,21 +7205,21 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>6869</v>
+        <v>7753</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>雲豹能源</t>
+          <t>星亞</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>65.87925383939816</v>
+        <v>70.89062056325089</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>67.8</v>
+        <v>37.2</v>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>49.79769715412034</v>
+        <v>40.3751952300271</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>16.06937845844141</v>
+        <v>7.754069261848411</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.3723114470895552</v>
+        <v>0.6812575911705968</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>0.3948658349704426</v>
+        <v>0.12056230864653</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7286,7 +7286,7 @@
         <v>46.15740156463294</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>6.983556567402799</v>
+        <v>6.983556592015375</v>
       </c>
       <c r="J129" s="2" t="n">
         <v>0.4585423421618823</v>
@@ -7301,7 +7301,7 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.026083535100273</v>
+        <v>-0.0260835351193529</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
